--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>105130</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>107556</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>603680.9901215534</v>
+        <v>603681</v>
       </c>
       <c r="R2" t="n">
-        <v>6743782.253397258</v>
+        <v>6743782</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -748,19 +743,9 @@
           <t>1998-09-13</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1998-09-13</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107556</v>
+        <v>107565</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107565</v>
+        <v>107577</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107577</v>
+        <v>107586</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107586</v>
+        <v>107591</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107591</v>
+        <v>107619</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107619</v>
+        <v>107625</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107625</v>
+        <v>107632</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107632</v>
+        <v>107636</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107636</v>
+        <v>107644</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107647</v>
+        <v>107652</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 9479-2025 artfynd.xlsx
+++ b/artfynd/A 9479-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>99206793</v>
       </c>
       <c r="B2" t="n">
-        <v>107652</v>
+        <v>107660</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
